--- a/01_analyses_states/Assam/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Assam/results/SoIB_summaries.xlsx
@@ -402,7 +402,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>10</v>
-      </c>
-      <c r="E3">
-        <v>16.2</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>28.6</v>
       </c>
       <c r="E4">
-        <v>67.59999999999999</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
         <v>4</v>
       </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
       <c r="D5">
-        <v>40</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E5">
-        <v>8.1</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="6">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>5.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C7">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C8">
-        <v>430</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C4">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C2">
-        <v>58.3</v>
+        <v>57.3</v>
       </c>
       <c r="D2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E2">
-        <v>80</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="3">
@@ -782,16 +782,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3">
-        <v>41.7</v>
+        <v>42.7</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>21.3</v>
       </c>
     </row>
   </sheetData>

--- a/01_analyses_states/Assam/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Assam/results/SoIB_summaries.xlsx
@@ -402,7 +402,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>10</v>
-      </c>
-      <c r="E3">
-        <v>16.1</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>28.6</v>
       </c>
       <c r="E4">
-        <v>67.7</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="5">
@@ -453,13 +453,13 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>50</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E5">
-        <v>6.5</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="6">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>6.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C7">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C8">
-        <v>430</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_states/Assam/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Assam/results/SoIB_summaries.xlsx
@@ -396,13 +396,13 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D4">
-        <v>28.6</v>
+        <v>85.7</v>
       </c>
       <c r="E4">
-        <v>73.3</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>71.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>13.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -472,13 +472,13 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C7">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="C8">
-        <v>423</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>565</v>
+        <v>558</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -706,7 +706,7 @@
         <v>142</v>
       </c>
       <c r="C4">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C2">
-        <v>57.3</v>
+        <v>61.2</v>
       </c>
       <c r="D2">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E2">
-        <v>78.7</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="3">
@@ -782,16 +782,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C3">
-        <v>42.7</v>
+        <v>38.8</v>
       </c>
       <c r="D3">
         <v>16</v>
       </c>
       <c r="E3">
-        <v>21.3</v>
+        <v>20.3</v>
       </c>
     </row>
   </sheetData>
